--- a/TP1/speedup/speedup_tp1.xlsx
+++ b/TP1/speedup/speedup_tp1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\octav\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D833F92-AA2C-4C32-B882-F41C33C8AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0999DEDD-460A-4772-9397-628F3D27BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C996D1BA-8A7A-4B9F-AECE-83BA1D0FD792}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>AMD Ryzen 9 5900X 12-Core</t>
   </si>
@@ -91,6 +91,20 @@
   <si>
     <t>Speedup (reference AMD Ryzen 3 3200G)</t>
   </si>
+  <si>
+    <t>Cores</t>
+  </si>
+  <si>
+    <t>Hilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejor rendimiento del
+AMD Ryzen 7 AI 350 por la mayor
+cantidad de hilos </t>
+  </si>
+  <si>
+    <t>Mejor opcion calidad precio AMD Ryzen 7 AI 350 (precio similar al Intel)</t>
+  </si>
 </sst>
 </file>
 
@@ -99,7 +113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +139,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -169,10 +191,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,10 +211,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -534,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC09BE59-201B-4667-B138-825AFBA6A93F}">
-  <dimension ref="A3:H21"/>
+  <dimension ref="A3:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="33.06640625" customWidth="1"/>
@@ -545,18 +576,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -564,17 +595,17 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="12">
         <v>77</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="13">
         <f>1/C7*100</f>
         <v>1.2987012987012987</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f>D7/D8</f>
         <v>1.0909090909090908</v>
       </c>
@@ -583,17 +614,17 @@
       <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="12">
         <v>84</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="13">
         <f t="shared" ref="D8:D9" si="0">1/C8*100</f>
         <v>1.1904761904761905</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f>D9/D8</f>
         <v>1.5</v>
       </c>
@@ -602,75 +633,106 @@
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="12">
         <v>56</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="13">
         <f t="shared" si="0"/>
         <v>1.7857142857142856</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="4"/>
-      <c r="H12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="D14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="10">
         <v>14.95</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="D15" s="12">
+        <v>4</v>
+      </c>
+      <c r="E15" s="12">
+        <v>4</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f>C15/C16</f>
         <v>7.5505050505050502</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="10">
         <v>1.98</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="D16" s="12">
+        <v>8</v>
+      </c>
+      <c r="E16" s="12">
+        <v>16</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f>C15/C17</f>
         <v>4.807073954983923</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="7" t="s">
+    <row r="17" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="10">
         <v>3.11</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
+      <c r="D17" s="12">
+        <v>8</v>
+      </c>
+      <c r="E17" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="2:5" ht="39" x14ac:dyDescent="0.45">
+      <c r="B20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="C31" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
